--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.6742239289306</v>
+        <v>14.08456138845122</v>
       </c>
       <c r="D2" t="n">
-        <v>84.76718050714848</v>
+        <v>13.77466683241163</v>
       </c>
       <c r="E2" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F2" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.94027816530541</v>
+        <v>8.92779520186213</v>
       </c>
       <c r="D3" t="n">
-        <v>50.22449601539073</v>
+        <v>8.161480602500994</v>
       </c>
       <c r="E3" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F3" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.94037291527291</v>
+        <v>7.302810598731848</v>
       </c>
       <c r="D4" t="n">
-        <v>43.44132933808112</v>
+        <v>7.059216017438182</v>
       </c>
       <c r="E4" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F4" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.01743988558632</v>
+        <v>5.365333981407777</v>
       </c>
       <c r="D5" t="n">
-        <v>27.82984010015149</v>
+        <v>4.522349016274617</v>
       </c>
       <c r="E5" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F5" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.75035743513861</v>
+        <v>4.021933083210025</v>
       </c>
       <c r="D6" t="n">
-        <v>22.19234102117215</v>
+        <v>3.606255415940474</v>
       </c>
       <c r="E6" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F6" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.71150412993683</v>
+        <v>7.915619421114735</v>
       </c>
       <c r="D7" t="n">
-        <v>47.71947769687091</v>
+        <v>7.754415125741523</v>
       </c>
       <c r="E7" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F7" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.50301715772585</v>
+        <v>3.331740288130451</v>
       </c>
       <c r="D8" t="n">
-        <v>21.63273185874532</v>
+        <v>3.515318927046114</v>
       </c>
       <c r="E8" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F8" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.05217139489861</v>
+        <v>1.633477851671025</v>
       </c>
       <c r="D9" t="n">
-        <v>14.88115170168796</v>
+        <v>2.418187151524294</v>
       </c>
       <c r="E9" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F9" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18655131818895</v>
+        <v>4.417814589205705</v>
       </c>
       <c r="D10" t="n">
-        <v>31.86933439072046</v>
+        <v>5.178766838492075</v>
       </c>
       <c r="E10" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F10" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.19765924006674</v>
+        <v>5.069619626510845</v>
       </c>
       <c r="D11" t="n">
-        <v>32.83254246117052</v>
+        <v>5.33528814994021</v>
       </c>
       <c r="E11" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F11" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.77078277246427</v>
+        <v>5.812752200525445</v>
       </c>
       <c r="D12" t="n">
-        <v>37.72287476481243</v>
+        <v>6.12996714928202</v>
       </c>
       <c r="E12" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F12" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.61966684720111</v>
+        <v>5.95069586267018</v>
       </c>
       <c r="D13" t="n">
-        <v>41.62586972782869</v>
+        <v>6.764203830772163</v>
       </c>
       <c r="E13" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F13" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.55829988776087</v>
+        <v>6.428223731761141</v>
       </c>
       <c r="D14" t="n">
-        <v>41.42053154804213</v>
+        <v>6.730836376556846</v>
       </c>
       <c r="E14" t="n">
-        <v>18.14295315149464</v>
+        <v>2.948229887117879</v>
       </c>
       <c r="F14" t="n">
-        <v>16.88022755533579</v>
+        <v>2.743036977742066</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
